--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 03/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 03/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.71685</v>
+        <v>16.44685</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47307</v>
+        <v>16.33965</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76058</v>
+        <v>16.36771</v>
       </c>
       <c r="F2" t="n">
-        <v>42.19529</v>
+        <v>42.35596</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05059</v>
+        <v>0.04948</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78083</v>
+        <v>1.79447</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.75038</v>
+        <v>16.40575</v>
       </c>
       <c r="D3" t="n">
-        <v>16.06669</v>
+        <v>16.18953</v>
       </c>
       <c r="E3" t="n">
-        <v>16.79838</v>
+        <v>16.21571</v>
       </c>
       <c r="F3" t="n">
-        <v>42.98065</v>
+        <v>41.49069</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05031</v>
+        <v>0.05039</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80165</v>
+        <v>1.81336</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.3926</v>
+        <v>16.72592</v>
       </c>
       <c r="D4" t="n">
-        <v>16.57568</v>
+        <v>16.14345</v>
       </c>
       <c r="E4" t="n">
-        <v>16.46211</v>
+        <v>16.49262</v>
       </c>
       <c r="F4" t="n">
-        <v>41.96602</v>
+        <v>42.76076</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05012</v>
+        <v>0.05013</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80792</v>
+        <v>1.76835</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.77466</v>
+        <v>16.84226</v>
       </c>
       <c r="D5" t="n">
-        <v>16.0353</v>
+        <v>16.4431</v>
       </c>
       <c r="E5" t="n">
-        <v>16.19767</v>
+        <v>16.54887</v>
       </c>
       <c r="F5" t="n">
-        <v>42.29283</v>
+        <v>42.82004</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05014</v>
+        <v>0.05008</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8306</v>
+        <v>1.77788</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.4883</v>
+        <v>16.99406</v>
       </c>
       <c r="D6" t="n">
-        <v>16.42541</v>
+        <v>16.18758</v>
       </c>
       <c r="E6" t="n">
-        <v>16.49489</v>
+        <v>16.25568</v>
       </c>
       <c r="F6" t="n">
-        <v>42.22922</v>
+        <v>42.03725</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04995</v>
+        <v>0.04924</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8313</v>
+        <v>1.79141</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.56686</v>
+        <v>16.51347</v>
       </c>
       <c r="D7" t="n">
-        <v>16.22776</v>
+        <v>16.37884</v>
       </c>
       <c r="E7" t="n">
-        <v>16.47727</v>
+        <v>16.41533</v>
       </c>
       <c r="F7" t="n">
-        <v>41.92728</v>
+        <v>41.62276</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0495</v>
+        <v>0.05007</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79474</v>
+        <v>1.82739</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.59071</v>
+        <v>16.59792</v>
       </c>
       <c r="D8" t="n">
-        <v>16.67494</v>
+        <v>16.08072</v>
       </c>
       <c r="E8" t="n">
-        <v>16.35497</v>
+        <v>16.20163</v>
       </c>
       <c r="F8" t="n">
-        <v>41.79194</v>
+        <v>41.29129</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05005</v>
+        <v>0.04839</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82955</v>
+        <v>1.80546</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.50323</v>
+        <v>16.98933</v>
       </c>
       <c r="D9" t="n">
-        <v>16.50609</v>
+        <v>16.4148</v>
       </c>
       <c r="E9" t="n">
-        <v>16.31424</v>
+        <v>16.91126</v>
       </c>
       <c r="F9" t="n">
-        <v>41.79316</v>
+        <v>41.98438</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04994</v>
+        <v>0.04984</v>
       </c>
       <c r="H9" t="n">
-        <v>1.77121</v>
+        <v>1.82544</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.59171</v>
+        <v>16.58219</v>
       </c>
       <c r="D10" t="n">
-        <v>16.04669</v>
+        <v>16.39965</v>
       </c>
       <c r="E10" t="n">
-        <v>16.23605</v>
+        <v>16.49713</v>
       </c>
       <c r="F10" t="n">
-        <v>43.35993</v>
+        <v>41.87896</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05194</v>
+        <v>0.04979</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81168</v>
+        <v>1.79041</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59615</v>
+        <v>0.60184</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09152</v>
+        <v>1.10961</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60412</v>
+        <v>0.60109</v>
       </c>
       <c r="D13" t="n">
-        <v>1.11261</v>
+        <v>1.08535</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60205</v>
+        <v>0.59388</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09</v>
+        <v>1.09056</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.58987</v>
+        <v>0.59981</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10435</v>
+        <v>1.09618</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62601</v>
+        <v>0.60062</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10587</v>
+        <v>1.10073</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59848</v>
+        <v>0.61458</v>
       </c>
       <c r="D17" t="n">
-        <v>1.12016</v>
+        <v>1.10073</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.59521</v>
+        <v>0.59563</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08005</v>
+        <v>1.08929</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60833</v>
+        <v>0.59984</v>
       </c>
       <c r="D19" t="n">
-        <v>1.09265</v>
+        <v>1.0672</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.58835</v>
+        <v>0.5990799999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09743</v>
+        <v>1.10196</v>
       </c>
     </row>
   </sheetData>
